--- a/public/excel/FT-CP-003.xlsx
+++ b/public/excel/FT-CP-003.xlsx
@@ -1,29 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDE5CA8-43E9-4FE4-84CA-DA20EFB7737F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5679970B-B904-4BF9-A03C-2C2BEE1AF1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22056" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMPROBACIONES" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -139,14 +126,15 @@
     <t>CUENTAS POR PAGAR</t>
   </si>
   <si>
-    <t>NOTA:  Este formato debe  acompañarse de los documentos originales que comprueben los movimientos listados</t>
+    <t>NOTA:  Este formato debe acompañarse de los documentos originales que comprueben los movimientos listados</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
@@ -159,12 +147,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -175,19 +157,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -213,26 +184,12 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF7A5128"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -241,6 +198,11 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -248,16 +210,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF7A5128"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -391,138 +380,143 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -588,9 +582,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -628,7 +622,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -734,7 +728,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -876,7 +870,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -891,8 +885,8 @@
     <col min="7" max="7" width="6.33203125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="5.44140625" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" customWidth="1"/>
+    <col min="11" max="11" width="4.109375" customWidth="1"/>
     <col min="12" max="12" width="10.6640625" customWidth="1"/>
     <col min="13" max="13" width="11.88671875" customWidth="1"/>
     <col min="14" max="17" width="5.6640625" customWidth="1"/>
@@ -923,10 +917,10 @@
       <c r="I1" s="42"/>
       <c r="J1" s="42"/>
       <c r="K1" s="42"/>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="17">
+      <c r="M1" s="10">
         <v>44298</v>
       </c>
     </row>
@@ -950,10 +944,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="43"/>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="19">
+      <c r="M2" s="12">
         <v>7.1</v>
       </c>
     </row>
@@ -971,10 +965,10 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -991,9 +985,9 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
       <c r="D6" s="3"/>
       <c r="E6" s="45"/>
       <c r="F6" s="46"/>
@@ -1007,99 +1001,102 @@
     </row>
     <row r="7" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
       <c r="K8" s="40"/>
       <c r="L8" s="40"/>
       <c r="M8" s="40"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="6" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="L9" s="7" t="s">
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="8"/>
+      <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="6" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="15" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="14"/>
+      <c r="L10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="11" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="36" t="s">
         <v>17</v>
       </c>
+      <c r="H11" s="36"/>
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="14"/>
+      <c r="L11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="17"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="12"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="M12" s="13"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="L13" t="s">
+      <c r="L13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="48">
         <f>I9+I10+I11</f>
         <v>0</v>
       </c>
@@ -1130,8 +1127,8 @@
       <c r="M14" s="29"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
@@ -1148,153 +1145,153 @@
       <c r="M15" s="30"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="25" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="26">
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="28">
         <f>SUM(L15:M15)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="26"/>
+      <c r="M16" s="28"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="27" t="s">
         <v>25</v>
       </c>
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
-      <c r="L17" s="26">
+      <c r="L17" s="28">
         <f>M13-L16</f>
         <v>0</v>
       </c>
-      <c r="M17" s="26"/>
+      <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="22"/>
@@ -1317,11 +1314,11 @@
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
       <c r="I26" s="24" t="s">
         <v>29</v>
       </c>
@@ -1331,64 +1328,64 @@
       <c r="M26" s="24"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
@@ -1408,7 +1405,7 @@
       <c r="M31" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="H8:J8"/>
@@ -1429,6 +1426,7 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:K14"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="I15:K15"/>
